--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/oct-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1305532-101-CM26</t>
+          <t>3776-516-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18445</v>
+        <v>1171.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>539119-3323-CM26</t>
+          <t>1305532-101-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1171.82</v>
+        <v>18445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3776-516-CM26</t>
+          <t>539119-3323-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4358-205-CM26</t>
+          <t>1233616-1906-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1315,27 +1315,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4308.94</v>
+        <v>46131.54</v>
       </c>
     </row>
     <row r="15">
@@ -1420,7 +1420,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233616-1906-CM26</t>
+          <t>4358-205-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1445,27 +1445,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>46131.54</v>
+        <v>4308.94</v>
       </c>
     </row>
     <row r="17">
@@ -1810,7 +1810,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1230771-41-CM26</t>
+          <t>623663-205-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.080.277-2</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1774.05</v>
+        <v>19693.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>701-631-CM26</t>
+          <t>1230771-41-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1900,27 +1900,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.080.277-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20230.48</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2982-90-CM26</t>
+          <t>701-631-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1965,27 +1965,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1999,72 +1999,263 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7481.38</v>
+        <v>20230.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2982-90-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>7481.38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3904-1167-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NextTime Software S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>99.576.370-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2627.52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>4931-123-CM26</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>65.613.130-6</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Intercity S.A.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>1719.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>717503-304-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.265.990-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Municipalidades</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>8255.860000000001</v>
       </c>
     </row>
   </sheetData>
